--- a/sos_all_assays.xlsx
+++ b/sos_all_assays.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tiabrown/Documents/git/cest-2.1-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307AEFDC-19A2-B94C-859B-72B0A63DF844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE589E25-D18D-0345-92CE-F652FD4A2119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="500" windowWidth="27360" windowHeight="16940" xr2:uid="{CF53EE06-8C5B-1647-8D2F-E4465C7625F6}"/>
   </bookViews>

--- a/sos_all_assays.xlsx
+++ b/sos_all_assays.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tiabrown/Documents/git/cest-2.1-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE589E25-D18D-0345-92CE-F652FD4A2119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F6D91A-67B9-454A-8668-DCC6755183D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="500" windowWidth="27360" windowHeight="16940" xr2:uid="{CF53EE06-8C5B-1647-8D2F-E4465C7625F6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="40">
   <si>
     <t>Strains</t>
   </si>
@@ -123,6 +123,39 @@
   </si>
   <si>
     <t>4mMTA S</t>
+  </si>
+  <si>
+    <t>fcmt-1</t>
+  </si>
+  <si>
+    <t>cest-1.2</t>
+  </si>
+  <si>
+    <t>cfa vs OP50</t>
+  </si>
+  <si>
+    <t>Bacteria</t>
+  </si>
+  <si>
+    <t>OP50</t>
+  </si>
+  <si>
+    <t>CFA and OP50</t>
+  </si>
+  <si>
+    <t>ges-1p::cest-2.1cDNA</t>
+  </si>
+  <si>
+    <t>cest-2.1(syb3900); moaEx2[cest-2.1p::cest-2.1gDNA::SL2::mcherry; coel::gfp]</t>
+  </si>
+  <si>
+    <t>Genotype</t>
+  </si>
+  <si>
+    <t>TIBR1 &amp; 2</t>
+  </si>
+  <si>
+    <t>Strain ID</t>
   </si>
 </sst>
 </file>
@@ -179,10 +212,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,14 +551,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9BA2D80-BF5C-8F43-B4ED-AF7A1A530888}">
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="13" max="13" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="68.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,132 +597,189 @@
         <v>14</v>
       </c>
       <c r="M1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" t="s">
         <v>16</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>1</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="T1" t="s">
+        <v>39</v>
+      </c>
+      <c r="U1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" s="1">
         <v>44413</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="T2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="1">
+      <c r="Q3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" s="1">
         <v>44418</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="T3" t="s">
+        <v>6</v>
+      </c>
+      <c r="U3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="1">
+      <c r="Q4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R4" s="1">
         <v>44435</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="O5" s="2">
+      <c r="Q5" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" s="2">
         <v>44439</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="O6" s="2">
+      <c r="Q6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R6" s="2">
         <v>44446</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R7" s="2">
         <v>44468</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="2">
+      <c r="Q8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" s="2">
         <v>44475</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="M9" t="s">
+      <c r="O9" t="s">
         <v>17</v>
       </c>
-      <c r="N9" t="s">
+      <c r="P9" t="s">
         <v>28</v>
       </c>
-      <c r="O9" s="2">
+      <c r="Q9" t="s">
+        <v>33</v>
+      </c>
+      <c r="R9" s="2">
         <v>44539</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="2">
+      <c r="Q10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R10" s="2">
         <v>44580</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="O11" s="2">
+      <c r="Q11" t="s">
+        <v>33</v>
+      </c>
+      <c r="R11" s="2">
         <v>44645</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -697,11 +789,14 @@
       <c r="C12" t="s">
         <v>5</v>
       </c>
-      <c r="O12" s="2">
+      <c r="Q12" t="s">
+        <v>33</v>
+      </c>
+      <c r="R12" s="2">
         <v>44656</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -711,11 +806,14 @@
       <c r="C13" t="s">
         <v>5</v>
       </c>
-      <c r="O13" s="2">
+      <c r="Q13" t="s">
+        <v>33</v>
+      </c>
+      <c r="R13" s="2">
         <v>44678</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -725,11 +823,14 @@
       <c r="C14" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="2">
+      <c r="Q14" t="s">
+        <v>33</v>
+      </c>
+      <c r="R14" s="2">
         <v>44691</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -739,22 +840,28 @@
       <c r="D15" t="s">
         <v>6</v>
       </c>
-      <c r="O15" s="2">
+      <c r="Q15" t="s">
+        <v>33</v>
+      </c>
+      <c r="R15" s="2">
         <v>44705</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>3</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
-      <c r="O16" s="2">
+      <c r="Q16" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="2">
         <v>44847</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -764,22 +871,28 @@
       <c r="C17" t="s">
         <v>5</v>
       </c>
-      <c r="O17" s="2">
+      <c r="Q17" t="s">
+        <v>33</v>
+      </c>
+      <c r="R17" s="2">
         <v>44909</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>3</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
-      <c r="O18" s="2">
+      <c r="Q18" t="s">
+        <v>33</v>
+      </c>
+      <c r="R18" s="2">
         <v>44959</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -789,11 +902,14 @@
       <c r="C19" t="s">
         <v>5</v>
       </c>
-      <c r="O19" s="2">
+      <c r="Q19" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" s="2">
         <v>44965</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -806,11 +922,14 @@
       <c r="E20" t="s">
         <v>7</v>
       </c>
-      <c r="O20" s="2">
+      <c r="Q20" t="s">
+        <v>33</v>
+      </c>
+      <c r="R20" s="2">
         <v>45054</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -820,11 +939,14 @@
       <c r="E21" t="s">
         <v>7</v>
       </c>
-      <c r="O21" s="2">
+      <c r="Q21" t="s">
+        <v>33</v>
+      </c>
+      <c r="R21" s="2">
         <v>45055</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -834,11 +956,14 @@
       <c r="C22" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="2">
+      <c r="Q22" t="s">
+        <v>33</v>
+      </c>
+      <c r="R22" s="2">
         <v>45056</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -854,11 +979,14 @@
       <c r="F23" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="2">
+      <c r="Q23" t="s">
+        <v>33</v>
+      </c>
+      <c r="R23" s="2">
         <v>45070</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -868,11 +996,14 @@
       <c r="E24" t="s">
         <v>7</v>
       </c>
-      <c r="O24" s="2">
+      <c r="Q24" t="s">
+        <v>33</v>
+      </c>
+      <c r="R24" s="2">
         <v>45096</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -882,11 +1013,14 @@
       <c r="C25" t="s">
         <v>5</v>
       </c>
-      <c r="O25" s="2">
+      <c r="Q25" t="s">
+        <v>33</v>
+      </c>
+      <c r="R25" s="2">
         <v>45099</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -899,11 +1033,14 @@
       <c r="F26" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="2">
+      <c r="Q26" t="s">
+        <v>33</v>
+      </c>
+      <c r="R26" s="2">
         <v>45100</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -916,11 +1053,14 @@
       <c r="G27" t="s">
         <v>9</v>
       </c>
-      <c r="O27" s="2">
+      <c r="Q27" t="s">
+        <v>33</v>
+      </c>
+      <c r="R27" s="2">
         <v>45103</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -930,11 +1070,14 @@
       <c r="G28" t="s">
         <v>9</v>
       </c>
-      <c r="O28" s="2">
+      <c r="Q28" t="s">
+        <v>33</v>
+      </c>
+      <c r="R28" s="2">
         <v>45106</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -944,11 +1087,14 @@
       <c r="G29" t="s">
         <v>9</v>
       </c>
-      <c r="O29" s="2">
+      <c r="Q29" t="s">
+        <v>33</v>
+      </c>
+      <c r="R29" s="2">
         <v>45175</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -958,11 +1104,14 @@
       <c r="G30" t="s">
         <v>9</v>
       </c>
-      <c r="O30" s="2">
+      <c r="Q30" t="s">
+        <v>33</v>
+      </c>
+      <c r="R30" s="2">
         <v>45175</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -972,11 +1121,14 @@
       <c r="G31" t="s">
         <v>9</v>
       </c>
-      <c r="O31" s="2">
+      <c r="Q31" t="s">
+        <v>33</v>
+      </c>
+      <c r="R31" s="2">
         <v>45175</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -992,11 +1144,14 @@
       <c r="J32" t="s">
         <v>12</v>
       </c>
-      <c r="O32" s="2">
+      <c r="Q32" t="s">
+        <v>33</v>
+      </c>
+      <c r="R32" s="2">
         <v>45403</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -1009,11 +1164,14 @@
       <c r="L33" t="s">
         <v>14</v>
       </c>
-      <c r="O33" s="2">
+      <c r="Q33" t="s">
+        <v>33</v>
+      </c>
+      <c r="R33" s="2">
         <v>45412</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -1029,11 +1187,14 @@
       <c r="J34" t="s">
         <v>12</v>
       </c>
-      <c r="O34" s="2">
+      <c r="Q34" t="s">
+        <v>33</v>
+      </c>
+      <c r="R34" s="2">
         <v>45407</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -1046,11 +1207,14 @@
       <c r="L35" t="s">
         <v>14</v>
       </c>
-      <c r="O35" s="2">
+      <c r="Q35" t="s">
+        <v>33</v>
+      </c>
+      <c r="R35" s="2">
         <v>45419</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -1063,11 +1227,14 @@
       <c r="L36" t="s">
         <v>14</v>
       </c>
-      <c r="O36" s="2">
+      <c r="Q36" t="s">
+        <v>33</v>
+      </c>
+      <c r="R36" s="2">
         <v>45422</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -1077,17 +1244,20 @@
       <c r="C37" t="s">
         <v>5</v>
       </c>
-      <c r="M37" t="s">
-        <v>18</v>
-      </c>
-      <c r="N37" t="s">
+      <c r="O37" t="s">
+        <v>18</v>
+      </c>
+      <c r="P37" t="s">
         <v>15</v>
       </c>
-      <c r="O37" s="2">
+      <c r="Q37" t="s">
+        <v>33</v>
+      </c>
+      <c r="R37" s="2">
         <v>45353</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -1097,17 +1267,20 @@
       <c r="C38" t="s">
         <v>5</v>
       </c>
-      <c r="M38" t="s">
-        <v>18</v>
-      </c>
-      <c r="N38" t="s">
+      <c r="O38" t="s">
+        <v>18</v>
+      </c>
+      <c r="P38" t="s">
         <v>19</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" t="s">
+        <v>33</v>
+      </c>
+      <c r="R38" s="2">
         <v>45312</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1117,17 +1290,20 @@
       <c r="C39" t="s">
         <v>5</v>
       </c>
-      <c r="M39" t="s">
-        <v>18</v>
-      </c>
-      <c r="N39" t="s">
+      <c r="O39" t="s">
+        <v>18</v>
+      </c>
+      <c r="P39" t="s">
         <v>19</v>
       </c>
-      <c r="O39" s="2">
+      <c r="Q39" t="s">
+        <v>33</v>
+      </c>
+      <c r="R39" s="2">
         <v>45321</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -1137,17 +1313,20 @@
       <c r="C40" t="s">
         <v>5</v>
       </c>
-      <c r="M40" t="s">
+      <c r="O40" t="s">
         <v>17</v>
       </c>
-      <c r="N40" t="s">
+      <c r="P40" t="s">
         <v>19</v>
       </c>
-      <c r="O40" s="2">
+      <c r="Q40" t="s">
+        <v>33</v>
+      </c>
+      <c r="R40" s="2">
         <v>45240</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1157,17 +1336,20 @@
       <c r="C41" t="s">
         <v>5</v>
       </c>
-      <c r="M41" t="s">
+      <c r="O41" t="s">
         <v>17</v>
       </c>
-      <c r="N41" t="s">
+      <c r="P41" t="s">
         <v>19</v>
       </c>
-      <c r="O41" s="2">
+      <c r="Q41" t="s">
+        <v>33</v>
+      </c>
+      <c r="R41" s="2">
         <v>45243</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -1177,17 +1359,20 @@
       <c r="C42" t="s">
         <v>5</v>
       </c>
-      <c r="M42" t="s">
-        <v>18</v>
-      </c>
-      <c r="N42" t="s">
+      <c r="O42" t="s">
+        <v>18</v>
+      </c>
+      <c r="P42" t="s">
         <v>19</v>
       </c>
-      <c r="O42" s="2">
+      <c r="Q42" t="s">
+        <v>33</v>
+      </c>
+      <c r="R42" s="2">
         <v>45353</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -1197,163 +1382,196 @@
       <c r="C43" t="s">
         <v>5</v>
       </c>
-      <c r="M43" t="s">
-        <v>18</v>
-      </c>
-      <c r="N43" t="s">
+      <c r="O43" t="s">
+        <v>18</v>
+      </c>
+      <c r="P43" t="s">
         <v>20</v>
       </c>
-      <c r="O43" s="2">
+      <c r="Q43" t="s">
+        <v>33</v>
+      </c>
+      <c r="R43" s="2">
         <v>45353</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C44" t="s">
         <v>5</v>
       </c>
-      <c r="M44" t="s">
-        <v>18</v>
-      </c>
-      <c r="N44" t="s">
+      <c r="O44" t="s">
+        <v>18</v>
+      </c>
+      <c r="P44" t="s">
         <v>21</v>
       </c>
-      <c r="O44" s="2">
+      <c r="Q44" t="s">
+        <v>33</v>
+      </c>
+      <c r="R44" s="2">
         <v>45362</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C45" t="s">
         <v>5</v>
       </c>
-      <c r="M45" t="s">
-        <v>18</v>
-      </c>
-      <c r="N45" t="s">
+      <c r="O45" t="s">
+        <v>18</v>
+      </c>
+      <c r="P45" t="s">
         <v>20</v>
       </c>
-      <c r="O45" s="2">
+      <c r="Q45" t="s">
+        <v>33</v>
+      </c>
+      <c r="R45" s="2">
         <v>45362</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C46" t="s">
         <v>5</v>
       </c>
-      <c r="M46" t="s">
-        <v>18</v>
-      </c>
-      <c r="N46" t="s">
+      <c r="O46" t="s">
+        <v>18</v>
+      </c>
+      <c r="P46" t="s">
         <v>22</v>
       </c>
-      <c r="O46" s="2">
+      <c r="Q46" t="s">
+        <v>33</v>
+      </c>
+      <c r="R46" s="2">
         <v>45362</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
         <v>5</v>
       </c>
-      <c r="M47" t="s">
-        <v>18</v>
-      </c>
-      <c r="N47" t="s">
+      <c r="O47" t="s">
+        <v>18</v>
+      </c>
+      <c r="P47" t="s">
         <v>23</v>
       </c>
-      <c r="O47" s="2">
+      <c r="Q47" t="s">
+        <v>33</v>
+      </c>
+      <c r="R47" s="2">
         <v>45362</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C48" t="s">
         <v>5</v>
       </c>
-      <c r="M48" t="s">
-        <v>18</v>
-      </c>
-      <c r="N48" t="s">
+      <c r="O48" t="s">
+        <v>18</v>
+      </c>
+      <c r="P48" t="s">
         <v>20</v>
       </c>
-      <c r="O48" s="2">
+      <c r="Q48" t="s">
+        <v>33</v>
+      </c>
+      <c r="R48" s="2">
         <v>45365</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C49" t="s">
         <v>5</v>
       </c>
-      <c r="M49" t="s">
-        <v>18</v>
-      </c>
-      <c r="N49" t="s">
+      <c r="O49" t="s">
+        <v>18</v>
+      </c>
+      <c r="P49" t="s">
         <v>24</v>
       </c>
-      <c r="O49" s="2">
+      <c r="Q49" t="s">
+        <v>33</v>
+      </c>
+      <c r="R49" s="2">
         <v>45365</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C50" t="s">
         <v>5</v>
       </c>
-      <c r="M50" t="s">
-        <v>18</v>
-      </c>
-      <c r="N50" t="s">
+      <c r="O50" t="s">
+        <v>18</v>
+      </c>
+      <c r="P50" t="s">
         <v>23</v>
       </c>
-      <c r="O50" s="2">
+      <c r="Q50" t="s">
+        <v>33</v>
+      </c>
+      <c r="R50" s="2">
         <v>45365</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C51" t="s">
         <v>5</v>
       </c>
-      <c r="M51" t="s">
-        <v>18</v>
-      </c>
-      <c r="N51" t="s">
+      <c r="O51" t="s">
+        <v>18</v>
+      </c>
+      <c r="P51" t="s">
         <v>25</v>
       </c>
-      <c r="O51" s="2">
+      <c r="Q51" t="s">
+        <v>33</v>
+      </c>
+      <c r="R51" s="2">
         <v>45365</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>3</v>
       </c>
       <c r="B52" t="s">
         <v>4</v>
       </c>
-      <c r="M52" t="s">
-        <v>18</v>
-      </c>
-      <c r="N52" t="s">
+      <c r="O52" t="s">
+        <v>18</v>
+      </c>
+      <c r="P52" t="s">
         <v>24</v>
       </c>
-      <c r="O52" s="2">
+      <c r="Q52" t="s">
+        <v>33</v>
+      </c>
+      <c r="R52" s="2">
         <v>45368</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>3</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
       </c>
-      <c r="M53" t="s">
-        <v>18</v>
-      </c>
-      <c r="N53" t="s">
+      <c r="O53" t="s">
+        <v>18</v>
+      </c>
+      <c r="P53" t="s">
         <v>25</v>
       </c>
-      <c r="O53" s="2">
+      <c r="Q53" t="s">
+        <v>33</v>
+      </c>
+      <c r="R53" s="2">
         <v>45368</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>3</v>
       </c>
@@ -1363,17 +1581,20 @@
       <c r="C54" t="s">
         <v>5</v>
       </c>
-      <c r="M54" t="s">
-        <v>18</v>
-      </c>
-      <c r="N54" t="s">
+      <c r="O54" t="s">
+        <v>18</v>
+      </c>
+      <c r="P54" t="s">
         <v>24</v>
       </c>
-      <c r="O54" s="2">
+      <c r="Q54" t="s">
+        <v>33</v>
+      </c>
+      <c r="R54" s="2">
         <v>45396</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -1383,17 +1604,20 @@
       <c r="C55" t="s">
         <v>5</v>
       </c>
-      <c r="M55" t="s">
-        <v>18</v>
-      </c>
-      <c r="N55" t="s">
+      <c r="O55" t="s">
+        <v>18</v>
+      </c>
+      <c r="P55" t="s">
         <v>25</v>
       </c>
-      <c r="O55" s="2">
+      <c r="Q55" t="s">
+        <v>33</v>
+      </c>
+      <c r="R55" s="2">
         <v>45396</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -1403,17 +1627,20 @@
       <c r="C56" t="s">
         <v>5</v>
       </c>
-      <c r="M56" t="s">
-        <v>18</v>
-      </c>
-      <c r="N56" t="s">
+      <c r="O56" t="s">
+        <v>18</v>
+      </c>
+      <c r="P56" t="s">
         <v>26</v>
       </c>
-      <c r="O56" s="2">
+      <c r="Q56" t="s">
+        <v>33</v>
+      </c>
+      <c r="R56" s="2">
         <v>45402</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -1423,17 +1650,20 @@
       <c r="C57" t="s">
         <v>5</v>
       </c>
-      <c r="M57" t="s">
-        <v>18</v>
-      </c>
-      <c r="N57" t="s">
+      <c r="O57" t="s">
+        <v>18</v>
+      </c>
+      <c r="P57" t="s">
         <v>27</v>
       </c>
-      <c r="O57" s="2">
+      <c r="Q57" t="s">
+        <v>33</v>
+      </c>
+      <c r="R57" s="2">
         <v>45412</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>3</v>
       </c>
@@ -1443,17 +1673,20 @@
       <c r="C58" t="s">
         <v>5</v>
       </c>
-      <c r="M58" t="s">
-        <v>18</v>
-      </c>
-      <c r="N58" t="s">
+      <c r="O58" t="s">
+        <v>18</v>
+      </c>
+      <c r="P58" t="s">
         <v>27</v>
       </c>
-      <c r="O58" s="2">
+      <c r="Q58" t="s">
+        <v>33</v>
+      </c>
+      <c r="R58" s="2">
         <v>45418</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>3</v>
       </c>
@@ -1463,14 +1696,80 @@
       <c r="C59" t="s">
         <v>5</v>
       </c>
-      <c r="M59" t="s">
-        <v>18</v>
-      </c>
-      <c r="N59" t="s">
+      <c r="O59" t="s">
+        <v>18</v>
+      </c>
+      <c r="P59" t="s">
         <v>27</v>
       </c>
-      <c r="O59" s="2">
+      <c r="Q59" t="s">
+        <v>33</v>
+      </c>
+      <c r="R59" s="2">
         <v>45426</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" t="s">
+        <v>29</v>
+      </c>
+      <c r="O60" t="s">
+        <v>18</v>
+      </c>
+      <c r="P60" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>34</v>
+      </c>
+      <c r="R60" s="3">
+        <v>45433</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+      <c r="E61" t="s">
+        <v>7</v>
+      </c>
+      <c r="N61" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>33</v>
+      </c>
+      <c r="R61" s="3">
+        <v>45433</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+      <c r="O62" t="s">
+        <v>18</v>
+      </c>
+      <c r="P62" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>33</v>
+      </c>
+      <c r="R62" s="3">
+        <v>45521</v>
       </c>
     </row>
   </sheetData>

--- a/sos_all_assays.xlsx
+++ b/sos_all_assays.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tiabrown/Documents/git/cest-2.1-Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F6D91A-67B9-454A-8668-DCC6755183D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DB672D-78F9-9D49-93C2-E5BFAE7B9090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="500" windowWidth="27360" windowHeight="16940" xr2:uid="{CF53EE06-8C5B-1647-8D2F-E4465C7625F6}"/>
   </bookViews>

--- a/sos_all_assays.xlsx
+++ b/sos_all_assays.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tiabrown/Documents/git/cest-2.1-Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tiabrown/Documents/git/cest-2.1-manuscript/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DB672D-78F9-9D49-93C2-E5BFAE7B9090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0DF00E-C380-8448-9F47-74D3DB917C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="500" windowWidth="27360" windowHeight="16940" xr2:uid="{CF53EE06-8C5B-1647-8D2F-E4465C7625F6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="41">
   <si>
     <t>Strains</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>Strain ID</t>
+  </si>
+  <si>
+    <t>40uMoglu</t>
   </si>
 </sst>
 </file>
@@ -551,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9BA2D80-BF5C-8F43-B4ED-AF7A1A530888}">
-  <dimension ref="A1:U62"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -1772,6 +1775,71 @@
         <v>45521</v>
       </c>
     </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+      <c r="P63" t="s">
+        <v>27</v>
+      </c>
+      <c r="R63" s="3">
+        <v>45528</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s">
+        <v>4</v>
+      </c>
+      <c r="P64" t="s">
+        <v>40</v>
+      </c>
+      <c r="R64" s="3">
+        <v>45532</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="P65" t="s">
+        <v>40</v>
+      </c>
+      <c r="R65" s="3">
+        <v>45533</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+      <c r="P66" t="s">
+        <v>40</v>
+      </c>
+      <c r="R66" s="3">
+        <v>45534</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
